--- a/PERSONAL/My Actions/Account Details.xlsx
+++ b/PERSONAL/My Actions/Account Details.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="11_86067E53175F904EC39DF2D0DB7836F615BA592D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF61A7C5-F0A5-410F-9BB5-114AB3344DC9}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>ID</t>
   </si>
@@ -35,16 +36,78 @@
   </si>
   <si>
     <t>Welcome01$</t>
+  </si>
+  <si>
+    <t>Standard Gateway Recovery Key:</t>
+  </si>
+  <si>
+    <t>Welcome$123</t>
+  </si>
+  <si>
+    <t>Vasanthkumar.m</t>
+  </si>
+  <si>
+    <t>Ma6imuthu</t>
+  </si>
+  <si>
+    <t>Electrical</t>
+  </si>
+  <si>
+    <t>Vasanth101742</t>
+  </si>
+  <si>
+    <t>Welcome$123*#</t>
+  </si>
+  <si>
+    <t>MediAssist</t>
+  </si>
+  <si>
+    <t>101742@ELGi</t>
+  </si>
+  <si>
+    <t>Mohana$123*#</t>
+  </si>
+  <si>
+    <t>ITR Filing</t>
+  </si>
+  <si>
+    <t>Indane</t>
+  </si>
+  <si>
+    <t>Mohana@123</t>
+  </si>
+  <si>
+    <t>https://nironline.ndml.in/nir-web/#/</t>
+  </si>
+  <si>
+    <t>K5255396</t>
+  </si>
+  <si>
+    <t>Eia :9102421191627</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -67,10 +130,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -78,8 +142,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -96,9 +167,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -136,9 +207,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -173,7 +244,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -208,7 +279,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -381,13 +452,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -420,7 +491,78 @@
         <v>6</v>
       </c>
     </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="3">
+        <v>9750833116</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A11" r:id="rId1" location="/" display="https://nironline.ndml.in/nir-web/ - /" xr:uid="{4D02B218-8FB8-40A5-A42C-95C7CA2C0D98}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
